--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.78600472635095</v>
+        <v>4.67772576803203</v>
       </c>
       <c r="D2" t="n">
-        <v>29.0824470446804</v>
+        <v>4.725897644760566</v>
       </c>
       <c r="E2" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F2" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00247632429053</v>
+        <v>4.225402402697211</v>
       </c>
       <c r="D3" t="n">
-        <v>26.45679704640676</v>
+        <v>4.299229520041099</v>
       </c>
       <c r="E3" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F3" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.76938295646482</v>
+        <v>5.325024730425533</v>
       </c>
       <c r="D4" t="n">
-        <v>33.27308902160817</v>
+        <v>5.406876966011328</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.40717232335847</v>
+        <v>6.891165502545751</v>
       </c>
       <c r="D5" t="n">
-        <v>42.85517830127045</v>
+        <v>6.963966473956448</v>
       </c>
       <c r="E5" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F5" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.81926376346748</v>
+        <v>8.745630361563466</v>
       </c>
       <c r="D6" t="n">
-        <v>54.05473084646167</v>
+        <v>8.78389376255002</v>
       </c>
       <c r="E6" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F6" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.33358344691312</v>
+        <v>8.016707310123383</v>
       </c>
       <c r="D7" t="n">
-        <v>49.31431985763788</v>
+        <v>8.013576976866156</v>
       </c>
       <c r="E7" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F7" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.47504512257517</v>
+        <v>7.552194832418466</v>
       </c>
       <c r="D8" t="n">
-        <v>46.28985404527648</v>
+        <v>7.522101282357428</v>
       </c>
       <c r="E8" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F8" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.31500000285532</v>
+        <v>7.36368750046399</v>
       </c>
       <c r="D9" t="n">
-        <v>45.29741068575254</v>
+        <v>7.360829236434788</v>
       </c>
       <c r="E9" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F9" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.6247837721136</v>
+        <v>7.251527362968461</v>
       </c>
       <c r="D10" t="n">
-        <v>45.1301336349439</v>
+        <v>7.333646715678384</v>
       </c>
       <c r="E10" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F10" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.82634322177158</v>
+        <v>4.846780773537882</v>
       </c>
       <c r="D11" t="n">
-        <v>30.7219011728904</v>
+        <v>4.99230894059469</v>
       </c>
       <c r="E11" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F11" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.19505548357564</v>
+        <v>6.369196516081042</v>
       </c>
       <c r="D12" t="n">
-        <v>39.56417818626765</v>
+        <v>6.429178955268494</v>
       </c>
       <c r="E12" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F12" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.24194747220181</v>
+        <v>2.314316464232794</v>
       </c>
       <c r="D13" t="n">
-        <v>14.78643308087115</v>
+        <v>2.402795375641561</v>
       </c>
       <c r="E13" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F13" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.36180551924217</v>
+        <v>5.258793396876854</v>
       </c>
       <c r="D14" t="n">
-        <v>32.81511977048302</v>
+        <v>5.332456962703492</v>
       </c>
       <c r="E14" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F14" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6.048944700249766</v>
+        <v>0.982953513790587</v>
       </c>
       <c r="D15" t="n">
-        <v>5.242301928438841</v>
+        <v>0.8518740633713117</v>
       </c>
       <c r="E15" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F15" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.27125560731753</v>
+        <v>5.4065790361891</v>
       </c>
       <c r="D16" t="n">
-        <v>32.57923695185961</v>
+        <v>5.294126004677186</v>
       </c>
       <c r="E16" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F16" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>50.12603785258592</v>
+        <v>8.145481151045212</v>
       </c>
       <c r="D17" t="n">
-        <v>50.5605969246738</v>
+        <v>8.216097000259492</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76856711432196</v>
+        <v>2.074892156077318</v>
       </c>
       <c r="F17" t="n">
-        <v>12.85130022246106</v>
+        <v>2.088336286149922</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
